--- a/backend/data/financials_by_company/146060.KQ.xlsx
+++ b/backend/data/financials_by_company/146060.KQ.xlsx
@@ -4351,10 +4351,8 @@
           <t>Siheung-si</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>15102</t>
-        </is>
+      <c r="C2" t="n">
+        <v>15102</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -4623,7 +4621,7 @@
         <v>-0.623</v>
       </c>
       <c r="CD2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CE2" t="n">
         <v>0.15054</v>
